--- a/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationDetailTemplate.xlsx
@@ -254,7 +254,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
     <numFmt numFmtId="178" formatCode="0.000000_ "/>
   </numFmts>
   <fonts count="21">

--- a/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationDetailTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <r>
       <rPr>
@@ -239,9 +239,6 @@
       </rPr>
       <t>产品成本</t>
     </r>
-  </si>
-  <si>
-    <t>币种（默认CNY）</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1200,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -1219,10 +1216,9 @@
     <col min="11" max="11" width="23.75" style="2" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="2" customWidth="1"/>
     <col min="13" max="13" width="17.375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1262,9 +1258,6 @@
       <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <r>
       <rPr>
@@ -81,6 +81,20 @@
         <scheme val="minor"/>
       </rPr>
       <t>SKU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>平台SKU</t>
     </r>
   </si>
   <si>
@@ -254,7 +268,7 @@
     <numFmt numFmtId="177" formatCode="0.0000_ "/>
     <numFmt numFmtId="178" formatCode="0.000000_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,6 +425,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1200,25 +1220,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="14.75" customWidth="1"/>
     <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="15.875" customWidth="1"/>
-    <col min="6" max="6" width="20.25" customWidth="1"/>
-    <col min="7" max="7" width="17.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="20.375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.375" style="3" customWidth="1"/>
+    <col min="5" max="6" width="15.875" customWidth="1"/>
+    <col min="7" max="7" width="20.25" customWidth="1"/>
+    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23.75" style="2" customWidth="1"/>
+    <col min="13" max="13" width="19.5" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17.375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1234,13 +1254,13 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="6" t="s">
@@ -1255,8 +1275,11 @@
       <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
